--- a/DOSSIES_MULTIFORMATO/SEMA/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SEMA/dossie.xlsx
@@ -636,7 +636,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020NE00361</t>
+          <t>2020NE00363</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3856.14</v>
+        <v>9000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020NE00363</t>
+          <t>2020NE00361</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9000</v>
+        <v>3856.14</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4º Termo Aditivo ao Contrato 10/2014 - CFPP - Prorrogação de prazo por 12 meses.</t>
+          <t>NE 270 DE 31/05/2017 NO VALOR DE R$ 174.000,00 4º TERMO ADITIVO AO CONTRATO 10/2014 - CFPP SUPRESSÃO DE 12,99%</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NE 270 DE 31/05/2017 NO VALOR DE R$ 174.000,00 4º TERMO ADITIVO AO CONTRATO 10/2014 - CFPP SUPRESSÃO DE 12,99%</t>
+          <t>4º Termo Aditivo ao Contrato 10/2014 - CFPP - Prorrogação de prazo por 12 meses.</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023NE0000325</t>
+          <t>2023NE0000324</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2879.46</v>
+        <v>317.76</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1119,14 +1119,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
+          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023NE0000324</t>
+          <t>2023NE0000325</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>317.76</v>
+        <v>2879.46</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1145,14 +1145,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
+          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2022NE0000583</t>
+          <t>2022NE0000585</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2456.76</v>
+        <v>5600</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1171,14 +1171,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anulação do Saldo da Nota de Empenho Nº 0020/2022, em atendimento ao Decreto Nº 46.621, de 11 de novembro de 2022.</t>
+          <t>Anulação do Saldo da Nota de Empenho Nº 0029/2022, em atendimento ao Decreto Nº 46.621, de 11 de novembro de 2022.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2022NE0000583</t>
+          <t>2022NE0000585</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2456.76</v>
+        <v>5600</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1197,14 +1197,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anulação do Saldo da Nota de Empenho Nº 0020/2022, em atendimento ao Decreto Nº 46.621, de 11 de novembro de 2022.</t>
+          <t>Anulação do Saldo da Nota de Empenho Nº 0029/2022, em atendimento ao Decreto Nº 46.621, de 11 de novembro de 2022.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2022NE0000585</t>
+          <t>2022NE0000583</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5600</v>
+        <v>2456.76</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1223,14 +1223,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anulação do Saldo da Nota de Empenho Nº 0029/2022, em atendimento ao Decreto Nº 46.621, de 11 de novembro de 2022.</t>
+          <t>Anulação do Saldo da Nota de Empenho Nº 0020/2022, em atendimento ao Decreto Nº 46.621, de 11 de novembro de 2022.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2022NE0000585</t>
+          <t>2022NE0000583</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5600</v>
+        <v>2456.76</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1249,14 +1249,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Anulação do Saldo da Nota de Empenho Nº 0029/2022, em atendimento ao Decreto Nº 46.621, de 11 de novembro de 2022.</t>
+          <t>Anulação do Saldo da Nota de Empenho Nº 0020/2022, em atendimento ao Decreto Nº 46.621, de 11 de novembro de 2022.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2018NE00435</t>
+          <t>2018NE00465</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8462.67</v>
+        <v>8032.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1275,14 +1275,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2018NE00463</t>
+          <t>2018NE00436</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31.12</v>
+        <v>613.95</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1301,14 +1301,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2018NE00442</t>
+          <t>2018NE00466</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7906.8</v>
+        <v>4744.08</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2018NE00466</t>
+          <t>2018NE00442</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4744.08</v>
+        <v>7906.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1379,14 +1379,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2018NE00436</t>
+          <t>2018NE00463</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>613.95</v>
+        <v>31.12</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1405,14 +1405,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2018NE00465</t>
+          <t>2018NE00435</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>8032.5</v>
+        <v>8462.67</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2015NE00103</t>
+          <t>2015NE00106</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4/2013</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12242.26</v>
+        <v>1500</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1697,14 +1697,14 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DESPESA RELATIVA AO SERVIÇO DE TRANSMISSÃO DE ACESSO A INTERNET NESTA SDS NO MÊS DE OUTUBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 04/13, CONFORME NFS-E N.º. 12274/14.</t>
+          <t>DESPESA RELATIVA AO SERVIÇO DE SISTEMA DE PROTOCOLO NO MÊS DE NOVEMBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 06/11, CONFORME NFS-E N.º. 12573/14.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2015NE00104</t>
+          <t>2015NE00105</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1989</v>
+        <v>33799.53</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1727,14 +1727,14 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>DESPESA RELATIVA AO SERVIÇO DE TRANSMISSÃO DE ACESSO A INTERNET DO PARQUE SUMAÚMA NO MÊS DE DEZEMBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 22/14, CONFORME NFS-E N.º. 12712/14</t>
+          <t>DESPESA RELATIVA AO SERVIÇO DE TRANSMISSÃO DE ACESSO A INTERNET DO PARQUE SUMAÚMA NOS MESES DE SETEMBRO, OUTUBRO E NOVEMBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 22/14, CONFORME NFS-E N.º. 12516/1251</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2015NE00111</t>
+          <t>2015NE00110</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1609.88</v>
+        <v>1986.48</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1757,19 +1757,19 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>DESPESA RELATIVA AO SERVIÇO DE MANUTENÇÃO PREVENTIVA E CORRETIVA NO MÊS DE NOVEMBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 02/14, CONFORME NFS-E N.º. 12515/14.</t>
+          <t>DESPESA RELATIVA AO SERVIÇO DE MANUTENÇÃO PREVENTIVA E CORRETIVA NO MÊS DE OUTUBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 02/14, CONFORME NFS-E N.º. 12273/14.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2015NE00102</t>
+          <t>2015NE00108</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4/2013</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12242.26</v>
+        <v>1500</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1787,19 +1787,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>DESPESA RELATIVA AO SERVIÇO DE TRANSMISSÃO DE ACESSO A INTERNET NESTA SDS NO MÊS DE DEZEMBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 04/13, CONFORME NFS-E N.º. 12711/14</t>
+          <t>DESPESA RELATIVA AO SERVIÇO DE SISTEMA DE PROTOCOLO VIA WEB (SPROWEB) NO MÊS DE OUTUBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 06/11, CONFORME NFS-E N.º. 12275/14.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2015NE00101</t>
+          <t>2015NE00107</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4/2013</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12242.26</v>
+        <v>1500</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>DESPESA RELATIVA AO SERVIÇO DE TRANSMISSÃO DE ACESSO A INTERNET NA SDS NO MÊS DE NOVEMBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 04/13, CONFORME NFS-E N.º. 12514/14.</t>
+          <t>DESPESA RELATIVA AO SERVIÇO DE SISTEMA DE PROTOCOLO VIA WEB (SPROWEB) NO MÊS DE DEZEMBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 06/11, CONFORME NFS-E N.º. 12958/14.</t>
         </is>
       </c>
     </row>
@@ -1854,12 +1854,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2015NE00107</t>
+          <t>2015NE00101</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>4/2013</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1500</v>
+        <v>12242.26</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,19 +1877,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>DESPESA RELATIVA AO SERVIÇO DE SISTEMA DE PROTOCOLO VIA WEB (SPROWEB) NO MÊS DE DEZEMBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 06/11, CONFORME NFS-E N.º. 12958/14.</t>
+          <t>DESPESA RELATIVA AO SERVIÇO DE TRANSMISSÃO DE ACESSO A INTERNET NA SDS NO MÊS DE NOVEMBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 04/13, CONFORME NFS-E N.º. 12514/14.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2015NE00108</t>
+          <t>2015NE00102</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>4/2013</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1500</v>
+        <v>12242.26</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1907,14 +1907,14 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>DESPESA RELATIVA AO SERVIÇO DE SISTEMA DE PROTOCOLO VIA WEB (SPROWEB) NO MÊS DE OUTUBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 06/11, CONFORME NFS-E N.º. 12275/14.</t>
+          <t>DESPESA RELATIVA AO SERVIÇO DE TRANSMISSÃO DE ACESSO A INTERNET NESTA SDS NO MÊS DE DEZEMBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 04/13, CONFORME NFS-E N.º. 12711/14</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2015NE00110</t>
+          <t>2015NE00111</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1986.48</v>
+        <v>1609.88</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1937,14 +1937,14 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>DESPESA RELATIVA AO SERVIÇO DE MANUTENÇÃO PREVENTIVA E CORRETIVA NO MÊS DE OUTUBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 02/14, CONFORME NFS-E N.º. 12273/14.</t>
+          <t>DESPESA RELATIVA AO SERVIÇO DE MANUTENÇÃO PREVENTIVA E CORRETIVA NO MÊS DE NOVEMBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 02/14, CONFORME NFS-E N.º. 12515/14.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2015NE00105</t>
+          <t>2015NE00104</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>33799.53</v>
+        <v>1989</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1967,19 +1967,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>DESPESA RELATIVA AO SERVIÇO DE TRANSMISSÃO DE ACESSO A INTERNET DO PARQUE SUMAÚMA NOS MESES DE SETEMBRO, OUTUBRO E NOVEMBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 22/14, CONFORME NFS-E N.º. 12516/1251</t>
+          <t>DESPESA RELATIVA AO SERVIÇO DE TRANSMISSÃO DE ACESSO A INTERNET DO PARQUE SUMAÚMA NO MÊS DE DEZEMBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 22/14, CONFORME NFS-E N.º. 12712/14</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2015NE00106</t>
+          <t>2015NE00103</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>4/2013</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1500</v>
+        <v>12242.26</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1997,17 +1997,21 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>DESPESA RELATIVA AO SERVIÇO DE SISTEMA DE PROTOCOLO NO MÊS DE NOVEMBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 06/11, CONFORME NFS-E N.º. 12573/14.</t>
+          <t>DESPESA RELATIVA AO SERVIÇO DE TRANSMISSÃO DE ACESSO A INTERNET NESTA SDS NO MÊS DE OUTUBRO/14, REFERENTE AO TERMO DE CONTRATO N.º 04/13, CONFORME NFS-E N.º. 12274/14.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2024NE0000315</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>2024NE0000314</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2/2020</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
           <t>26/08/2024</t>
@@ -2023,21 +2027,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anulação da Nota de Empenho Nº 314, para alteração do valor empenhado.</t>
+          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2024NE0000314</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2/2020</t>
-        </is>
-      </c>
+          <t>2024NE0000315</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>26/08/2024</t>
@@ -2053,19 +2053,19 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
+          <t>Anulação da Nota de Empenho Nº 314, para alteração do valor empenhado.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2023NE00181</t>
+          <t>2023NE00182</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5/2021</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>317.76</v>
+        <v>2879.46</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2083,19 +2083,19 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Serviço de VPN</t>
+          <t>Execução de Sistema SPROWEB</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2023NE0000181</t>
+          <t>2023NE0000182</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5/2021</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>317.76</v>
+        <v>2879.46</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2113,19 +2113,19 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
+          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2023NE0000182</t>
+          <t>2023NE0000181</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2021</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2879.46</v>
+        <v>317.76</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2143,19 +2143,19 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
+          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2023NE00182</t>
+          <t>2023NE00181</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2021</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2879.46</v>
+        <v>317.76</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Execução de Sistema SPROWEB</t>
+          <t>Serviço de VPN</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2240,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2020NE00324</t>
+          <t>2020NE00325</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>8032.5</v>
+        <v>31.12</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2259,14 +2259,14 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Despesa de Exercícios Anteriores referente ao serviço de Acesso Gerenciado a Rede Mundial , CT. 12/2018, mês de dezembro/2018.</t>
+          <t>Despesa de Exercícios Anteriores referente ao serviço de e sistemas de Protocolo-SPPROWEB) CT. 01/2017, mês de dezembro/2018.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2020NE00323</t>
+          <t>2020NE00315</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1581.36</v>
+        <v>3424.34</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2285,14 +2285,14 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Despesa de Exercícios Anteriores referente ao serviço de licenças de uso de sistemas de informação-Gestor de Conteudo WEB, CT. 05/2018, mês de outubro/2018.</t>
+          <t>Indenização da despesa sem cobertura contratual referente aos serviços prestados de licença de uso de VPN para atender o processamento da Folha de Pagamento desta SEMA, nos meses de abril à setembro/2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2020NE00327</t>
+          <t>2020NE00326</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1632.01</v>
+        <v>1581.36</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pagamento a PRODAM Processamento de Dados Amazonas S/A, pelos serviços prestados no Sistema de Protocolo WEB, conforme Nota Fiscal 12505 - mês de dezembro/2019 - RD 003/2020.</t>
+          <t>Despesa de Exercícios Anteriores referente ao serviço de licenças de uso de sistemas de informação-Gestor de Conteudo WEB, CT. 05/2018, mês de novembro/2018.</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2020NE00326</t>
+          <t>2020NE00327</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1581.36</v>
+        <v>1632.01</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2363,14 +2363,14 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Despesa de Exercícios Anteriores referente ao serviço de licenças de uso de sistemas de informação-Gestor de Conteudo WEB, CT. 05/2018, mês de novembro/2018.</t>
+          <t>Pagamento a PRODAM Processamento de Dados Amazonas S/A, pelos serviços prestados no Sistema de Protocolo WEB, conforme Nota Fiscal 12505 - mês de dezembro/2019 - RD 003/2020.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2020NE00315</t>
+          <t>2020NE00323</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3424.34</v>
+        <v>1581.36</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2389,14 +2389,14 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Indenização da despesa sem cobertura contratual referente aos serviços prestados de licença de uso de VPN para atender o processamento da Folha de Pagamento desta SEMA, nos meses de abril à setembro/2</t>
+          <t>Despesa de Exercícios Anteriores referente ao serviço de licenças de uso de sistemas de informação-Gestor de Conteudo WEB, CT. 05/2018, mês de outubro/2018.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2020NE00325</t>
+          <t>2020NE00324</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>31.12</v>
+        <v>8032.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Despesa de Exercícios Anteriores referente ao serviço de e sistemas de Protocolo-SPPROWEB) CT. 01/2017, mês de dezembro/2018.</t>
+          <t>Despesa de Exercícios Anteriores referente ao serviço de Acesso Gerenciado a Rede Mundial , CT. 12/2018, mês de dezembro/2018.</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2594,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2015NE00236</t>
+          <t>2015NE00241</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>10/2014</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>4124.18</v>
+        <v>320000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2617,19 +2617,19 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Complemento cobertura financeira 2015</t>
+          <t>Complemento Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2015NE00241</t>
+          <t>2015NE00236</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>10/2014</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>320000</v>
+        <v>4124.18</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Complemento Cobertura Financeira 2015</t>
+          <t>Complemento cobertura financeira 2015</t>
         </is>
       </c>
     </row>
@@ -2684,17 +2684,21 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2018NE00083</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
+          <t>2018NE00092</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>4/2013</t>
+        </is>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
           <t>21/02/2018</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11015.49</v>
+        <v>21152.25</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2703,19 +2707,19 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇO PARA CRIAÇÃO DO SITE BILÍNGUE</t>
+          <t>Internet</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2018NE00094</t>
+          <t>2018NE00081</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>4/2013</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2724,7 +2728,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>613.95</v>
+        <v>21152.25</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2733,28 +2737,24 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SPROWEB</t>
+          <t>Contratação de Serviço de acesso a rede de internet.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2018NE00084</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>1/2017</t>
-        </is>
-      </c>
+          <t>2018NE00091</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
           <t>21/02/2018</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>19478.96</v>
+        <v>613.95</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2763,24 +2763,28 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>contratação de serviço de acesso ao protocolo SPROWEB</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2018NE00089</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>2018NE00082</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1/2017</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr">
         <is>
           <t>21/02/2018</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>19478.96</v>
+        <v>613.95</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2789,14 +2793,14 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SEMA</t>
+          <t>contratação de serviço de acesso ao SPROWEB, sistema de protocolo.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2018NE00093</t>
+          <t>2018NE00095</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2810,7 +2814,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>19478.96</v>
+        <v>11015.49</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2819,14 +2823,14 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SPROWEB</t>
+          <t>CONTRATO N.º 15/2017, SERVIÇO DE SITE</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2018NE00090</t>
+          <t>2018NE00088</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -2836,7 +2840,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>21152.25</v>
+        <v>11015.49</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2845,14 +2849,14 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>anulação</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2018NE00088</t>
+          <t>2018NE00090</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -2862,7 +2866,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11015.49</v>
+        <v>21152.25</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2871,14 +2875,14 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>anulação</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2018NE00095</t>
+          <t>2018NE00093</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2892,7 +2896,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11015.49</v>
+        <v>19478.96</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2901,28 +2905,24 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CONTRATO N.º 15/2017, SERVIÇO DE SITE</t>
+          <t>SPROWEB</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2018NE00082</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>1/2017</t>
-        </is>
-      </c>
+          <t>2018NE00089</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
           <t>21/02/2018</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>613.95</v>
+        <v>19478.96</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2931,24 +2931,28 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>contratação de serviço de acesso ao SPROWEB, sistema de protocolo.</t>
+          <t>SEMA</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2018NE00091</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>2018NE00084</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1/2017</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
           <t>21/02/2018</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>613.95</v>
+        <v>19478.96</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2957,19 +2961,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>contratação de serviço de acesso ao protocolo SPROWEB</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2018NE00081</t>
+          <t>2018NE00094</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4/2013</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2978,7 +2982,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21152.25</v>
+        <v>613.95</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2987,28 +2991,24 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de acesso a rede de internet.</t>
+          <t>SPROWEB</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2018NE00092</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>4/2013</t>
-        </is>
-      </c>
+          <t>2018NE00083</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
           <t>21/02/2018</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21152.25</v>
+        <v>11015.49</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3017,17 +3017,21 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>CONTRATAÇÃO DE SERVIÇO PARA CRIAÇÃO DO SITE BILÍNGUE</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2021NE0000018</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>2021NE0000002</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2/2020</t>
+        </is>
+      </c>
       <c r="C86" t="inlineStr">
         <is>
           <t>21/01/2021</t>
@@ -3043,21 +3047,17 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NOTA DE EMPENHO No. 2021NE0000002, PARA CORREÇÃO NA DATA DA EMISSÃO.</t>
+          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades de registro eletrônico, acesso a localização e disponibilização de histórico de trâmites d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2021NE0000002</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2/2020</t>
-        </is>
-      </c>
+          <t>2021NE0000018</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
           <t>21/01/2021</t>
@@ -3073,14 +3073,14 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades de registro eletrônico, acesso a localização e disponibilização de histórico de trâmites d</t>
+          <t>ANULAÇÃO DA NOTA DE EMPENHO No. 2021NE0000002, PARA CORREÇÃO NA DATA DA EMISSÃO.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2019NE00510</t>
+          <t>2019NE00516</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>3162.72</v>
+        <v>3.42</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3099,14 +3099,14 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NOTA DE EMPENHO Nº 2019NE0001, POR ENCERRAMENTO DA VIGÊNCIA DO TERMO DE CONTRATO.</t>
+          <t>ANULAÇÃO DO SALDO DA NOTA DE EMPENHO Nº 2019NE00136, POR ENCERRAMENTO DO EXERCÍCIO, CONFORME ESTABELECIDO NO DECRETO Nº 41.554, DE 26 DE NOVEMBRO DE 2019, EM SEU ANEXO ÚNICO.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2019NE00516</t>
+          <t>2019NE00510</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3.42</v>
+        <v>3162.72</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NOTA DE EMPENHO Nº 2019NE00136, POR ENCERRAMENTO DO EXERCÍCIO, CONFORME ESTABELECIDO NO DECRETO Nº 41.554, DE 26 DE NOVEMBRO DE 2019, EM SEU ANEXO ÚNICO.</t>
+          <t>ANULAÇÃO DO SALDO DA NOTA DE EMPENHO Nº 2019NE0001, POR ENCERRAMENTO DA VIGÊNCIA DO TERMO DE CONTRATO.</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2017NE00452</t>
+          <t>2017NE00439</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3288,7 +3288,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>8851.74</v>
+        <v>2677.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2017NE00439</t>
+          <t>2017NE00452</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2677.5</v>
+        <v>8851.74</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3472,21 +3472,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2024NE0000524</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>38/2023</t>
-        </is>
-      </c>
+          <t>2024NE0000525</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
           <t>16/12/2024</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>8455.690000000001</v>
+        <v>2717.66</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3495,24 +3491,28 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Contratação de Empresa esp. em serviços de Uso de Sist. de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web para publicação de informações, notícias, vídeos e imagens via website</t>
+          <t>Anulação total da Nota de Empenho Nº 502, emitida em 26/11/2024, devido a celebração do 1º termo aditivo do termo de Contrato Nº 38/2023 - PRODAM PROCESSAMENTO DE DADOS AMAZONAS S A, no mês de Dezembr</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2024NE0000525</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+          <t>2024NE0000524</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>38/2023</t>
+        </is>
+      </c>
       <c r="C103" t="inlineStr">
         <is>
           <t>16/12/2024</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2717.66</v>
+        <v>8455.690000000001</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3521,19 +3521,19 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Anulação total da Nota de Empenho Nº 502, emitida em 26/11/2024, devido a celebração do 1º termo aditivo do termo de Contrato Nº 38/2023 - PRODAM PROCESSAMENTO DE DADOS AMAZONAS S A, no mês de Dezembr</t>
+          <t>Contratação de Empresa esp. em serviços de Uso de Sist. de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web para publicação de informações, notícias, vídeos e imagens via website</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2016NE00395</t>
+          <t>2016NE00396</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4/2013</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10187.39</v>
+        <v>1860.46</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3558,12 +3558,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2016NE00396</t>
+          <t>2016NE00395</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>4/2013</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1860.46</v>
+        <v>10187.39</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2017NE00158</t>
+          <t>2017NE00159</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -3719,14 +3719,14 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>REFORÇO</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2017NE00159</t>
+          <t>2017NE00158</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>REFORÇO</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
@@ -3782,12 +3782,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2024NE0000064</t>
+          <t>2024NE0000063</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5/2021</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>317.76</v>
+        <v>2879.46</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3805,19 +3805,19 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
+          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2024NE0000063</t>
+          <t>2024NE0000064</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2021</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2879.46</v>
+        <v>317.76</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
+          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2017NE00025</t>
+          <t>2017NE00027</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3954,7 +3954,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2017NE00027</t>
+          <t>2017NE00025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4130,12 +4130,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2023NE0000639</t>
+          <t>2023NE0000630</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2021</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1439.73</v>
+        <v>158.88</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
+          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
         </is>
       </c>
     </row>
@@ -4190,12 +4190,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2023NE0000630</t>
+          <t>2023NE0000639</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5/2021</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4204,7 +4204,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>158.88</v>
+        <v>1439.73</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
+          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
         </is>
       </c>
     </row>
@@ -4310,12 +4310,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2021NE0000223</t>
+          <t>2021NE0000220</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5/2021</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>515.52</v>
+        <v>9265.799999999999</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4333,19 +4333,19 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforço a Nota de Empenho Nº 2021NE000075, complemento do Contrato nº 05/2021 - Prestação de serviços de VPN (Virtual Private Network), necessário para acessar sistemas específicos do Estado, no caso </t>
+          <t>Reforço a Nota de Empenho Nº 2021NE000089, do 1º Termo Aditivo ao Termo de Contrato Nº 002/2020, para prorrogação do prazo pelo período de 12 (doze) meses + reequilíbrio financeiro, referente a presta</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2021NE0000220</t>
+          <t>2021NE0000223</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2021</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>9265.799999999999</v>
+        <v>515.52</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Reforço a Nota de Empenho Nº 2021NE000089, do 1º Termo Aditivo ao Termo de Contrato Nº 002/2020, para prorrogação do prazo pelo período de 12 (doze) meses + reequilíbrio financeiro, referente a presta</t>
+          <t xml:space="preserve">Reforço a Nota de Empenho Nº 2021NE000075, complemento do Contrato nº 05/2021 - Prestação de serviços de VPN (Virtual Private Network), necessário para acessar sistemas específicos do Estado, no caso </t>
         </is>
       </c>
     </row>
@@ -4456,12 +4456,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2019NE00406</t>
+          <t>2019NE00411</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>4/2018</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>5528.07</v>
+        <v>25917.06</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4479,19 +4479,19 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>REFORÇO A NOTA DE EMPENHO 2019NE00018, DESEMBOLSO DE OUTUBRO, NOVEMBRO E DEZEMBRO DO 3º TERMO ADITIVO AO CONTRATO 001/2017.</t>
+          <t>Reforço referente Saldo do 1º Termo Aditivo ao Termo de Contrato nº 004/2018, referente serviços de sistema de rede, contemplando o acesso a rede mundial de internet.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2019NE00411</t>
+          <t>2019NE00406</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>4/2018</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>25917.06</v>
+        <v>5528.07</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Reforço referente Saldo do 1º Termo Aditivo ao Termo de Contrato nº 004/2018, referente serviços de sistema de rede, contemplando o acesso a rede mundial de internet.</t>
+          <t>REFORÇO A NOTA DE EMPENHO 2019NE00018, DESEMBOLSO DE OUTUBRO, NOVEMBRO E DEZEMBRO DO 3º TERMO ADITIVO AO CONTRATO 001/2017.</t>
         </is>
       </c>
     </row>
@@ -4632,12 +4632,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2024NE0000461</t>
+          <t>2024NE0000444</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2021</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4646,7 +4646,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1439.73</v>
+        <v>317.76</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
+          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
         </is>
       </c>
     </row>
@@ -4692,12 +4692,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2024NE0000444</t>
+          <t>2024NE0000461</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5/2021</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>317.76</v>
+        <v>1439.73</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
+          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2025NE0000078</t>
+          <t>2025NE0000079</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5/2021</t>
+          <t>38/2023</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4856,7 +4856,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>317.76</v>
+        <v>16911.38</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
+          <t>Contratação de Empresa esp. em serviços de Uso de Sist. de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web para publicação de informações, notícias, vídeos e imagens via website</t>
         </is>
       </c>
     </row>
@@ -4902,12 +4902,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2025NE0000079</t>
+          <t>2025NE0000078</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>38/2023</t>
+          <t>5/2021</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>16911.38</v>
+        <v>317.76</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Contratação de Empresa esp. em serviços de Uso de Sist. de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web para publicação de informações, notícias, vídeos e imagens via website</t>
+          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
         </is>
       </c>
     </row>
@@ -4962,12 +4962,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2024NE0000440</t>
+          <t>2024NE0000439</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5/2021</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>317.76</v>
+        <v>2879.46</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -4985,19 +4985,19 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
+          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2024NE0000439</t>
+          <t>2024NE0000440</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2021</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2879.46</v>
+        <v>317.76</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5015,19 +5015,19 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
+          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2025NE01088</t>
+          <t>2025NE0000443</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>17/2025</t>
+          <t>38/2023</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>713425.66</v>
+        <v>8455.690000000001</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5045,19 +5045,19 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Implantação, manutenção evolutiva e corretiva, suporte técnico, gestão e treinamento do Sistema Eletrônico de Informações - SEI</t>
+          <t>Contratação de Empresa esp. em serviços de Uso de Sist. de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web para publicação de informações, notícias, vídeos e imagens via website</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2025NE0000443</t>
+          <t>2025NE01088</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>38/2023</t>
+          <t>17/2025</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5066,7 +5066,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>8455.690000000001</v>
+        <v>713425.66</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5075,19 +5075,19 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Contratação de Empresa esp. em serviços de Uso de Sist. de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web para publicação de informações, notícias, vídeos e imagens via website</t>
+          <t>Implantação, manutenção evolutiva e corretiva, suporte técnico, gestão e treinamento do Sistema Eletrônico de Informações - SEI</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2023NE0000536</t>
+          <t>2023NE0000537</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2021</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5096,7 +5096,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2879.46</v>
+        <v>317.76</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5105,19 +5105,19 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
+          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2023NE0000537</t>
+          <t>2023NE0000536</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5/2021</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5126,7 +5126,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>317.76</v>
+        <v>2879.46</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
+          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
         </is>
       </c>
     </row>
@@ -5262,12 +5262,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2015NE00045</t>
+          <t>2015NE00018</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>4/2013</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>6624.45</v>
+        <v>24484.52</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5285,14 +5285,14 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL PARA ACERTO QUANTO AO REAJUSTE COM BASE NO IGPM.</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2015NE00017</t>
+          <t>2015NE00046</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>6624.45</v>
+        <v>6566.31</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5315,19 +5315,19 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>3º TERMO DE ADITAMENTO AO CONTRATO Nº 006/2011, POR MAIS 12 MESES COM REAJUSTE DE 4,88% NO VALOR, ENTRE ESTA SDS E A EMPRESA PRODAM PROCESSAMENTO DE DADOS PARA O SERVIÇO DE PROTOCOLO DIGITAL (SPROWEB)</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2015NE00009</t>
+          <t>2015NE00011</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>22/2014</t>
+          <t>2/2014</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5336,7 +5336,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>5967</v>
+        <v>2000</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5352,12 +5352,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2015NE00011</t>
+          <t>2015NE00009</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2/2014</t>
+          <t>22/2014</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>2000</v>
+        <v>5967</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2015NE00046</t>
+          <t>2015NE00017</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>6566.31</v>
+        <v>6624.45</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5405,19 +5405,19 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>3º TERMO DE ADITAMENTO AO CONTRATO Nº 006/2011, POR MAIS 12 MESES COM REAJUSTE DE 4,88% NO VALOR, ENTRE ESTA SDS E A EMPRESA PRODAM PROCESSAMENTO DE DADOS PARA O SERVIÇO DE PROTOCOLO DIGITAL (SPROWEB)</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2015NE00018</t>
+          <t>2015NE00045</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>4/2013</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>24484.52</v>
+        <v>6624.45</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>ANULAÇÃO TOTAL PARA ACERTO QUANTO AO REAJUSTE COM BASE NO IGPM.</t>
         </is>
       </c>
     </row>
@@ -5532,12 +5532,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2016NE00028</t>
+          <t>2016NE00015</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>4/2013</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>11162.76</v>
+        <v>19587.62</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5555,19 +5555,19 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇO DO SISTEMA DE PROTOCOLO INFORMATIZADO EM PLATAFORMA WEB (SPROWEB).</t>
+          <t>CONTRATAÇÃO DE SERVIÇO DE TELECOMUNICAÇÃO, PARA PROVER SERVIÇOS DE CONEXÃO DEDICADOS E EXCLUSIVOS A REDE DE INTERNET VIA FIBRA ÓTICA EM DIVERSAS VELOCIDADES, COM SUPRESSÃO DE 20%.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2016NE00015</t>
+          <t>2016NE00028</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>4/2013</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5576,7 +5576,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>19587.62</v>
+        <v>11162.76</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5585,14 +5585,14 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇO DE TELECOMUNICAÇÃO, PARA PROVER SERVIÇOS DE CONEXÃO DEDICADOS E EXCLUSIVOS A REDE DE INTERNET VIA FIBRA ÓTICA EM DIVERSAS VELOCIDADES, COM SUPRESSÃO DE 20%.</t>
+          <t>CONTRATAÇÃO DE SERVIÇO DO SISTEMA DE PROTOCOLO INFORMATIZADO EM PLATAFORMA WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2015NE00662</t>
+          <t>2015NE00661</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -5602,7 +5602,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>7387.73</v>
+        <v>9883.629999999999</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2015NE00661</t>
+          <t>2015NE00662</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>9883.629999999999</v>
+        <v>7387.73</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5644,12 +5644,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2025NE0000610</t>
+          <t>2025NE0000609</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5/2021</t>
+          <t>2/2025</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>339.14</v>
+        <v>2748.84</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -5667,19 +5667,19 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
+          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2025NE0000609</t>
+          <t>2025NE0000610</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2/2025</t>
+          <t>5/2021</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>2748.84</v>
+        <v>339.14</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5697,19 +5697,19 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
+          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2022NE0000459</t>
+          <t>2022NE0000458</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5/2021</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>150.67</v>
+        <v>1365.32</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5727,19 +5727,19 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Reforço a Nota de Empenho nº 2022NE000149, contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que</t>
+          <t>Reforço a Nota de Empenho Nº 2022NE000166, Parte do Saldo do 2º Termo Aditivo ao Contrato n.º 002/2020, serviços de Sistema de Protocolo em Plataforma Web (Sproweb), para atender as necessidades de re</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2022NE0000458</t>
+          <t>2022NE0000459</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2021</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5748,7 +5748,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1365.32</v>
+        <v>150.67</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -5757,19 +5757,19 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Reforço a Nota de Empenho Nº 2022NE000166, Parte do Saldo do 2º Termo Aditivo ao Contrato n.º 002/2020, serviços de Sistema de Protocolo em Plataforma Web (Sproweb), para atender as necessidades de re</t>
+          <t>Reforço a Nota de Empenho nº 2022NE000149, contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2025NE0000442</t>
+          <t>2025NE0000441</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>5/2021</t>
+          <t>2/2025</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>169.57</v>
+        <v>1374.42</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -5787,19 +5787,19 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
+          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2025NE0000441</t>
+          <t>2025NE0000442</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2/2025</t>
+          <t>5/2021</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1374.42</v>
+        <v>169.57</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -5817,28 +5817,24 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
+          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2016NE00355</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>6/2011</t>
-        </is>
-      </c>
+          <t>2016NE00353</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
         <is>
           <t>03/10/2016</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1860.46</v>
+        <v>10867.2</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -5847,28 +5843,24 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>REFORÇO DO MÊS DE OUTUBRO/2016</t>
+          <t>REFORÇO MÊS DE OUTUBRO/16</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2016NE00353</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>4/2013</t>
-        </is>
-      </c>
+          <t>2016NE00355</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
           <t>03/10/2016</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>10867.2</v>
+        <v>1860.46</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -5877,24 +5869,28 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>REFORÇO MÊS DE OUTUBRO/16</t>
+          <t>REFORÇO DO MÊS DE OUTUBRO/2016</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2016NE00355</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr"/>
+          <t>2016NE00353</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>4/2013</t>
+        </is>
+      </c>
       <c r="C184" t="inlineStr">
         <is>
           <t>03/10/2016</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1860.46</v>
+        <v>10867.2</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -5903,24 +5899,28 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>REFORÇO DO MÊS DE OUTUBRO/2016</t>
+          <t>REFORÇO MÊS DE OUTUBRO/16</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2016NE00353</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr"/>
+          <t>2016NE00355</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>6/2011</t>
+        </is>
+      </c>
       <c r="C185" t="inlineStr">
         <is>
           <t>03/10/2016</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>10867.2</v>
+        <v>1860.46</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>REFORÇO MÊS DE OUTUBRO/16</t>
+          <t>REFORÇO DO MÊS DE OUTUBRO/2016</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2015NE00537</t>
+          <t>2015NE00539</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>22/2014</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5980,7 +5980,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1888.11</v>
+        <v>3580.2</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -5989,19 +5989,19 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL PARA AJUSTE ORÇAMENTÁRIO</t>
+          <t>REFORÇO da ne 326/15 A FIM DE COBRIR O SALDO DESCOBERTO DO TERMO DE CONTRATO, CONSIDERANDO DP/ 565-15 EMITIDO PELA PRODAM PROCESSAMENTO DE DADOS ÀS FLS. 37 E NOTA TÉCNICA Nº 02/15-GETI/SEMA ÀS FLS. 38</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2015NE00539</t>
+          <t>2015NE00537</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>22/2014</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>3580.2</v>
+        <v>1888.11</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>REFORÇO da ne 326/15 A FIM DE COBRIR O SALDO DESCOBERTO DO TERMO DE CONTRATO, CONSIDERANDO DP/ 565-15 EMITIDO PELA PRODAM PROCESSAMENTO DE DADOS ÀS FLS. 37 E NOTA TÉCNICA Nº 02/15-GETI/SEMA ÀS FLS. 38</t>
+          <t>ANULAÇÃO TOTAL PARA AJUSTE ORÇAMENTÁRIO</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Serviço de Execução de Sistemas PRODAM-RH</t>
+          <t>NE 300 DE 03/06/2019 NO VALOR DE R$ 814.458,00 - REFERENTE AO CONTRATO 009/2019 - PRODAM RH - SEMAD</t>
         </is>
       </c>
     </row>
@@ -6079,19 +6079,19 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>NE 300 DE 03/06/2019 NO VALOR DE R$ 814.458,00 - REFERENTE AO CONTRATO 009/2019 - PRODAM RH - SEMAD</t>
+          <t>Serviço de Execução de Sistemas PRODAM-RH</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2022NE0000021</t>
+          <t>2022NE0000020</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>5/2021</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>515.52</v>
+        <v>9265.799999999999</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma.</t>
+          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades de registro eletrônico, acesso a localização e disponibilização de histórico de trâmites d</t>
         </is>
       </c>
     </row>
@@ -6146,12 +6146,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2022NE0000020</t>
+          <t>2022NE0000021</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2021</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>9265.799999999999</v>
+        <v>515.52</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades de registro eletrônico, acesso a localização e disponibilização de histórico de trâmites d</t>
+          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma.</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2018NE00166</t>
+          <t>2018NE00169</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>4/2018</t>
+          <t>5/2018</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>64260</v>
+        <v>12650.88</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6349,19 +6349,19 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>contratação de serviço de gerenciamento e acesso a internet.</t>
+          <t>SERVIÇO DE CONTRATAÇÃO DO SITE DESTA SEMA</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2018NE00169</t>
+          <t>2018NE00166</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>5/2018</t>
+          <t>4/2018</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>12650.88</v>
+        <v>64260</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6379,28 +6379,24 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>SERVIÇO DE CONTRATAÇÃO DO SITE DESTA SEMA</t>
+          <t>contratação de serviço de gerenciamento e acesso a internet.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2017NE00141</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>4/2013</t>
-        </is>
-      </c>
+          <t>2017NE00140</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
       <c r="C201" t="inlineStr">
         <is>
           <t>02/05/2017</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>42840</v>
+        <v>7441.84</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6409,24 +6405,28 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇO DE CONEXÃO DA INTERNET</t>
+          <t>E SPROWEB</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2017NE00140</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr"/>
+          <t>2017NE00141</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>4/2013</t>
+        </is>
+      </c>
       <c r="C202" t="inlineStr">
         <is>
           <t>02/05/2017</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>7441.84</v>
+        <v>42840</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6435,19 +6435,19 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>E SPROWEB</t>
+          <t>CONTRATAÇÃO DE SERVIÇO DE CONEXÃO DA INTERNET</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2015NE00144</t>
+          <t>2015NE00145</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2/2014</t>
+          <t>4/2013</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>4146</v>
+        <v>12691.55</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6465,19 +6465,19 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL TENDO EM VISTA QUE ESTA SECRETARIA NÃO MANIFESTOU INTERESSE EM PRORROGAR O CONTRATO Nº 002/14.</t>
+          <t>Cobertura Financeira 2015 - Março</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2015NE00145</t>
+          <t>2015NE00144</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>4/2013</t>
+          <t>2/2014</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>12691.55</v>
+        <v>4146</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015 - Março</t>
+          <t>ANULAÇÃO TOTAL TENDO EM VISTA QUE ESTA SECRETARIA NÃO MANIFESTOU INTERESSE EM PRORROGAR O CONTRATO Nº 002/14.</t>
         </is>
       </c>
     </row>
@@ -6592,12 +6592,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2024NE0000006</t>
+          <t>2024NE0000005</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>5/2021</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6606,7 +6606,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>317.76</v>
+        <v>2879.46</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -6615,19 +6615,19 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
+          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2024NE0000005</t>
+          <t>2024NE0000006</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>5/2021</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>2879.46</v>
+        <v>317.76</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -6645,14 +6645,14 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB(SPROWEB), p/ atender as necessidades de registro eletrônico, acesso a localização e disp. de histórico de trâmites de doc. e proce</t>
+          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma, Parece</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2023NE0000003</t>
+          <t>2023NE0000002</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>602.6799999999999</v>
+        <v>5461.28</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -6671,14 +6671,14 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma.</t>
+          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades de registro eletrônico, acesso a localização e disponibilização de histórico de trâmites d</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2023NE0000002</t>
+          <t>2023NE0000003</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>5461.28</v>
+        <v>602.6799999999999</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -6697,19 +6697,19 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades de registro eletrônico, acesso a localização e disponibilização de histórico de trâmites d</t>
+          <t>Contratação para prestação de serviços de VPN (Virtual Private Network), para acessar sistemas específicos do Estado, no caso em tela Folha de Pagamento, que é armazenado no mainframe da mesma.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2020NE00005</t>
+          <t>2020NE00001</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>4/2018</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>34844.05</v>
+        <v>613.95</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -6727,19 +6727,19 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Serviços de sistema de rede, contemplando o acesso a gerenciamento a rede mundial de internet através da rede de Governo.</t>
+          <t>Execução de Sistema de Informação - Serviço de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades de registro eletrônico, acesso a localização e disponibilização de histórico de trâmi</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2020NE00001</t>
+          <t>2020NE00005</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>4/2018</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6748,7 +6748,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>613.95</v>
+        <v>34844.05</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6757,19 +6757,19 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Execução de Sistema de Informação - Serviço de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades de registro eletrônico, acesso a localização e disponibilização de histórico de trâmi</t>
+          <t>Serviços de sistema de rede, contemplando o acesso a gerenciamento a rede mundial de internet através da rede de Governo.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2019NE00077</t>
+          <t>2019NE00005</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>10/2014</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>640000</v>
+        <v>613.96</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6787,19 +6787,19 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CFPP</t>
+          <t>contratação de serviço de acesso ao protocolo SPROWEB</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2019NE00078</t>
+          <t>2019NE00004</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>6/2016</t>
+          <t>4/2018</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6808,7 +6808,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>8000</v>
+        <v>24097.5</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -6817,19 +6817,19 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Serviços Eventuais</t>
+          <t>contratação de serviço de gerenciamento e acesso a internet.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2019NE00029</t>
+          <t>2019NE00001</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>10/2014</t>
+          <t>5/2018</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6838,7 +6838,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>339162.4</v>
+        <v>4744.08</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -6847,19 +6847,19 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Cobertura Financeira do 6 º Termo Aditivo</t>
+          <t>SERVIÇO DE CONTRATAÇÃO DO SITE DESTA SEMA</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2019NE00001</t>
+          <t>2019NE00029</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>5/2018</t>
+          <t>10/2014</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>4744.08</v>
+        <v>339162.4</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -6877,19 +6877,19 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>SERVIÇO DE CONTRATAÇÃO DO SITE DESTA SEMA</t>
+          <t>Cobertura Financeira do 6 º Termo Aditivo</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2019NE00004</t>
+          <t>2019NE00078</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>4/2018</t>
+          <t>6/2016</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6898,7 +6898,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>24097.5</v>
+        <v>8000</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -6907,19 +6907,19 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>contratação de serviço de gerenciamento e acesso a internet.</t>
+          <t>Serviços Eventuais</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2019NE00005</t>
+          <t>2019NE00077</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>10/2014</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>613.96</v>
+        <v>640000</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -6937,24 +6937,28 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>contratação de serviço de acesso ao protocolo SPROWEB</t>
+          <t>CFPP</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2018NE00047</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr"/>
+          <t>2018NE00042</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>4/2013</t>
+        </is>
+      </c>
       <c r="C220" t="inlineStr">
         <is>
           <t>02/01/2018</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>11015.49</v>
+        <v>21152.25</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -6963,14 +6967,14 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇO PARA CRIAÇÃO DO SITE BILÍNGUE</t>
+          <t>Contratação de Serviço de acesso a rede de internet.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2018NE00043</t>
+          <t>2018NE00048</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6984,7 +6988,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>613.95</v>
+        <v>19478.96</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -6993,14 +6997,14 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>contratação de serviço de acesso ao SPROWEB, sistema de protocolo.</t>
+          <t>contratação de serviço de acesso ao protocolo SPROWEB</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2018NE00048</t>
+          <t>2018NE00043</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7014,7 +7018,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>19478.96</v>
+        <v>613.95</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7023,28 +7027,24 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>contratação de serviço de acesso ao protocolo SPROWEB</t>
+          <t>contratação de serviço de acesso ao SPROWEB, sistema de protocolo.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2018NE00042</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>4/2013</t>
-        </is>
-      </c>
+          <t>2018NE00047</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
         <is>
           <t>02/01/2018</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>21152.25</v>
+        <v>11015.49</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de acesso a rede de internet.</t>
+          <t>CONTRATAÇÃO DE SERVIÇO PARA CRIAÇÃO DO SITE BILÍNGUE</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2017NE00126</t>
+          <t>2017NE00098</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -7104,7 +7104,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>584000</v>
+        <v>373940.6</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2017NE00098</t>
+          <t>2017NE00126</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -7134,7 +7134,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>373940.6</v>
+        <v>584000</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7180,12 +7180,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2014NE00004</t>
+          <t>2014NE00024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>4/2013</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7194,7 +7194,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>23203.68</v>
+        <v>25264.8</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7203,19 +7203,19 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Contrato No. 4/2013 - Acesso a rede Internet com banda de 4Mbps</t>
+          <t>Contrato No. 6/2011 - Cessão de Uso do SproWeb</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2014NE00024</t>
+          <t>2014NE00004</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>4/2013</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>25264.8</v>
+        <v>23203.68</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7233,14 +7233,14 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Contrato No. 6/2011 - Cessão de Uso do SproWeb</t>
+          <t>Contrato No. 4/2013 - Acesso a rede Internet com banda de 4Mbps</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2017NE00391</t>
+          <t>2017NE00393</t>
         </is>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -7250,7 +7250,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1860.46</v>
+        <v>1475.29</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7259,14 +7259,14 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇO ESPECIALIZADO NA EXECUÇÃO DO SISTEMA SPROWEB.</t>
+          <t>CONTRATAÇÃO DE SERVIÇO PARA CRIAÇÃO DO SITE BILÍNGUE</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2017NE00379</t>
+          <t>2017NE00394</t>
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -7276,7 +7276,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>13387.5</v>
+        <v>10710</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO PARA AJUSTE.</t>
+          <t>CONTRATAÇÃO DE SERVIÇO DE CONEXÃO DA INTERNET</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7318,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2017NE00394</t>
+          <t>2017NE00379</t>
         </is>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>10710</v>
+        <v>13387.5</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7337,14 +7337,14 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇO DE CONEXÃO DA INTERNET</t>
+          <t>ANULAÇÃO DE EMPENHO PARA AJUSTE.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2017NE00393</t>
+          <t>2017NE00391</t>
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1475.29</v>
+        <v>1860.46</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇO PARA CRIAÇÃO DO SITE BILÍNGUE</t>
+          <t>CONTRATAÇÃO DE SERVIÇO ESPECIALIZADO NA EXECUÇÃO DO SISTEMA SPROWEB.</t>
         </is>
       </c>
     </row>
@@ -7400,21 +7400,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2017NE00346</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>1/2017</t>
-        </is>
-      </c>
+          <t>2017NE00345</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
       <c r="C236" t="inlineStr">
         <is>
           <t>01/11/2017</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1860.46</v>
+        <v>1475.29</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7423,7 +7419,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇO ESPECIALIZADO NA EXECUÇÃO DO SISTEMA SPROWEB.</t>
+          <t>CONTRATAÇÃO DE SERVIÇO PARA CRIAÇÃO DO SITE BILÍNGUE</t>
         </is>
       </c>
     </row>
@@ -7456,17 +7452,21 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2017NE00345</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr"/>
+          <t>2017NE00346</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>1/2017</t>
+        </is>
+      </c>
       <c r="C238" t="inlineStr">
         <is>
           <t>01/11/2017</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1475.29</v>
+        <v>1860.46</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -7475,19 +7475,19 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇO PARA CRIAÇÃO DO SITE BILÍNGUE</t>
+          <t>CONTRATAÇÃO DE SERVIÇO ESPECIALIZADO NA EXECUÇÃO DO SISTEMA SPROWEB.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2016NE00360</t>
+          <t>2016NE00361</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>4/2013</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7496,7 +7496,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1860.46</v>
+        <v>10867.2</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -7512,12 +7512,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2016NE00361</t>
+          <t>2016NE00360</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>4/2013</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>10867.2</v>
+        <v>1860.46</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2017NE00290</t>
+          <t>2017NE00291</t>
         </is>
       </c>
       <c r="B241" t="inlineStr"/>
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>3720.92</v>
+        <v>21420</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇO ESPECIALIZADO NA EXECUÇÃO DO SISTEMA SPROWEB.</t>
+          <t>CONTRATAÇÃO DE SERVIÇO DE CONEXÃO DA INTERNET</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2017NE00291</t>
+          <t>2017NE00290</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>21420</v>
+        <v>3720.92</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -7613,19 +7613,19 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇO DE CONEXÃO DA INTERNET</t>
+          <t>CONTRATAÇÃO DE SERVIÇO ESPECIALIZADO NA EXECUÇÃO DO SISTEMA SPROWEB.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2016NE00312</t>
+          <t>2016NE00311</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>4/2013</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>5581.38</v>
+        <v>32601.6</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -7643,19 +7643,19 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>REFORÇO A NOTA DE EMPENHO Nº 2016NE00028, CORRESPONDENTE AO CONTRATO Nº 006/2011, EM SEU 5º TERMO ADITIVO.</t>
+          <t>REFORÇO DA NOTA DE EMPENHO Nº 2016NE00167, REFERENTE AO CONTRATO Nº 004/2013.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2016NE00311</t>
+          <t>2016NE00312</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>4/2013</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7664,7 +7664,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>32601.6</v>
+        <v>5581.38</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -7673,14 +7673,14 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>REFORÇO DA NOTA DE EMPENHO Nº 2016NE00167, REFERENTE AO CONTRATO Nº 004/2013.</t>
+          <t>REFORÇO A NOTA DE EMPENHO Nº 2016NE00028, CORRESPONDENTE AO CONTRATO Nº 006/2011, EM SEU 5º TERMO ADITIVO.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2019NE00294</t>
+          <t>2019NE00293</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -7690,7 +7690,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>25917.06</v>
+        <v>5528.07</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2019NE00293</t>
+          <t>2019NE00294</t>
         </is>
       </c>
       <c r="B247" t="inlineStr"/>
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>5528.07</v>
+        <v>25917.06</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2019NE00089</t>
+          <t>2019NE00088</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>5528.07</v>
+        <v>8300.25</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -7841,14 +7841,14 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Contratação de serviço do Sistema Sproweb</t>
+          <t>contratação de serviço de gerenciamento e acesso a internet.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2019NE00088</t>
+          <t>2019NE00089</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>8300.25</v>
+        <v>5528.07</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -7867,19 +7867,19 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>contratação de serviço de gerenciamento e acesso a internet.</t>
+          <t>Contratação de serviço do Sistema Sproweb</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2015NE00272</t>
+          <t>2015NE00327</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>4/2013</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -7888,7 +7888,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>449.29</v>
+        <v>16744.13</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -7897,19 +7897,19 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Cobertura Financeira abril 2015</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2015NE00325</t>
+          <t>2015NE00326</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>4/2013</t>
+          <t>22/2014</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -7918,7 +7918,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>88144.28999999999</v>
+        <v>6364.8</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -7927,19 +7927,19 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>1º TERMO DE ADITAMENTO AO CONTRATO Nº 22/2014, COM SUPRESSÃO DE 20% NO VALOR, FIRMADO ENTRE ESTA SECRETARIA DE ESTADO DO MEIO SEMA E A EMPRESA PRODAM PROCESSAMENTO DE DADOS, COM O OBJETIVO DE PROVER S</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2015NE00326</t>
+          <t>2015NE00325</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>22/2014</t>
+          <t>4/2013</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>6364.8</v>
+        <v>88144.28999999999</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -7957,19 +7957,19 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>1º TERMO DE ADITAMENTO AO CONTRATO Nº 22/2014, COM SUPRESSÃO DE 20% NO VALOR, FIRMADO ENTRE ESTA SECRETARIA DE ESTADO DO MEIO SEMA E A EMPRESA PRODAM PROCESSAMENTO DE DADOS, COM O OBJETIVO DE PROVER S</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2015NE00327</t>
+          <t>2015NE00272</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>4/2013</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>16744.13</v>
+        <v>449.29</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>Cobertura Financeira abril 2015</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2018NE00059</t>
+          <t>2018NE00058</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>11015.49</v>
+        <v>19478.96</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2018NE00057</t>
+          <t>2018NE00056</t>
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>613.95</v>
+        <v>21152.25</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -8065,14 +8065,14 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>anulação</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2018NE00056</t>
+          <t>2018NE00057</t>
         </is>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>21152.25</v>
+        <v>613.95</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -8091,14 +8091,14 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>anulação</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2018NE00058</t>
+          <t>2018NE00059</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -8108,7 +8108,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>19478.96</v>
+        <v>11015.49</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2016NE00049</t>
+          <t>2016NE00051</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>3118.8</v>
+        <v>1559.4</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>SERVIÇO DE INTERNET MESES DE OUT E NOV/15</t>
+          <t>SERVIÇO DE INTERNET MÊS DE DEZEMBRO/15</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8184,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2016NE00051</t>
+          <t>2016NE00049</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>1559.4</v>
+        <v>3118.8</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>SERVIÇO DE INTERNET MÊS DE DEZEMBRO/15</t>
+          <t>SERVIÇO DE INTERNET MESES DE OUT E NOV/15</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8931,6 +8931,474 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SEMAD-MANAUS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>009/2019</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>121314</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>12/2020</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>465.404,58</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1905 dias</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SEMAD-MANAUS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>009/2019</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>129504</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12/2021</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>424.595,97</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1542 dias</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SEMAD-MANAUS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>007/2023</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>155111</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>11/2024</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>389.549,95</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>471 dias</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SEMAD-MANAUS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>007/2023</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>155724</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>679.938,71</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>448 dias</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SEMAD-MANAUS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>007/2023</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>163832</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>10/2025</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>439.209,02</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>140 dias</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SEMAD-MANAUS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Licença de uso de sistemas de informação</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>009/2021</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>164660</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>11/2025</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3.922,88</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>107 dias</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SEMAD-MANAUS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>007/2023</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>164760</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>11/2025</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>445.615,44</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>105 dias</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SEMAD-MANAUS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>007/2023</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>165509</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>776.814,69</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>80 dias</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SEMAD-MANAUS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Implantação de Sistemas de Informação</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>017/2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>165653</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>213.718,26</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>72 dias</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DOSSIES_MULTIFORMATO/SEMA/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SEMA/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2029-01-31</t>
         </is>
       </c>
     </row>
